--- a/data/trans_orig/BARTHEL_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2007</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51100</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58916</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77676</t>
+          <t>78063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87716</t>
+          <t>87781</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>47329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57195</t>
+          <t>57155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>65497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17694</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60058</t>
+          <t>59889</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>69155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23126</t>
+          <t>23129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78336</t>
+          <t>77811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90597</t>
+          <t>90262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>32456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20721</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40962</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227736</t>
+          <t>227616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245210</t>
+          <t>245164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72297</t>
+          <t>72347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82641</t>
+          <t>82661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304862</t>
+          <t>303356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325103</t>
+          <t>324826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>28647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35310</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42032</t>
+          <t>41131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51862</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69106</t>
+          <t>67603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85434</t>
+          <t>84835</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116405</t>
+          <t>116193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134534</t>
+          <t>135129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41868</t>
+          <t>42085</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70407</t>
+          <t>69927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42318</t>
+          <t>40545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>71356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>354663</t>
+          <t>355143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>383202</t>
+          <t>382985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356271</t>
+          <t>357359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>386397</t>
+          <t>388170</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29442</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52120</t>
+          <t>52277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74229</t>
+          <t>73382</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111261</t>
+          <t>109071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109232</t>
+          <t>111958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152505</t>
+          <t>155046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>449431</t>
+          <t>449274</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>472109</t>
+          <t>471783</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>565581</t>
+          <t>567771</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>602613</t>
+          <t>603460</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1025888</t>
+          <t>1023347</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1069161</t>
+          <t>1066435</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2012</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32836</t>
+          <t>33137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56702</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68073</t>
+          <t>68119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17284</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47089</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59430</t>
+          <t>58709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62247</t>
+          <t>62302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76087</t>
+          <t>76028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>32938</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98884</t>
+          <t>99831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113495</t>
+          <t>113580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35727</t>
+          <t>35536</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48260</t>
+          <t>48346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140497</t>
+          <t>140330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159338</t>
+          <t>159605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35240</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61947</t>
+          <t>62267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>20763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48959</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77738</t>
+          <t>78742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169806</t>
+          <t>169486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196513</t>
+          <t>196494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>39332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52575</t>
+          <t>51905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214110</t>
+          <t>213106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242889</t>
+          <t>243729</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51263</t>
+          <t>51296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77652</t>
+          <t>77971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64989</t>
+          <t>65797</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95213</t>
+          <t>96909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78481</t>
+          <t>77924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93293</t>
+          <t>93229</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110748</t>
+          <t>110429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137137</t>
+          <t>137104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>195883</t>
+          <t>194187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226107</t>
+          <t>225299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80181</t>
+          <t>79062</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116224</t>
+          <t>114756</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>79475</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115265</t>
+          <t>112808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278480</t>
+          <t>279948</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>314523</t>
+          <t>315642</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>281427</t>
+          <t>283884</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>317188</t>
+          <t>317217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65298</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>101241</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167183</t>
+          <t>168229</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216612</t>
+          <t>215483</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246732</t>
+          <t>245762</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>305712</t>
+          <t>309472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>456251</t>
+          <t>458396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>494339</t>
+          <t>494362</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>525393</t>
+          <t>526522</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>574822</t>
+          <t>573776</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>995930</t>
+          <t>992170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1054910</t>
+          <t>1055880</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2016</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59262</t>
+          <t>58162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>67878</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92188</t>
+          <t>92918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103479</t>
+          <t>103380</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12744</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>20667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>49868</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51097</t>
+          <t>50265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64588</t>
+          <t>64400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>13510</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28366</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102359</t>
+          <t>102488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114348</t>
+          <t>113944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31989</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42863</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138104</t>
+          <t>138742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154639</t>
+          <t>154778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>13660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30312</t>
+          <t>29804</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56727</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173544</t>
+          <t>174052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189368</t>
+          <t>190196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68765</t>
+          <t>67032</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86274</t>
+          <t>86415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246175</t>
+          <t>248682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272031</t>
+          <t>273121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>19141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37448</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26048</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>48693</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49481</t>
+          <t>50078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79552</t>
+          <t>79596</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107773</t>
+          <t>107042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125744</t>
+          <t>126080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112065</t>
+          <t>110857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133502</t>
+          <t>134066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225219</t>
+          <t>225175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255290</t>
+          <t>254693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,57%</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77727</t>
+          <t>77971</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116289</t>
+          <t>116582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77727</t>
+          <t>77971</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116289</t>
+          <t>116582</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296794</t>
+          <t>296501</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>335356</t>
+          <t>335112</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>296794</t>
+          <t>296501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>335356</t>
+          <t>335112</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56089</t>
+          <t>56165</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85115</t>
+          <t>86052</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145578</t>
+          <t>144350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195661</t>
+          <t>195689</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>209483</t>
+          <t>210555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>270902</t>
+          <t>269768</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>506213</t>
+          <t>505276</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>535239</t>
+          <t>535163</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>576703</t>
+          <t>576675</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>626786</t>
+          <t>628014</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1092790</t>
+          <t>1093924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1154209</t>
+          <t>1153137</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2023</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97772</t>
+          <t>97173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104765</t>
+          <t>104426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56222</t>
+          <t>56598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62686</t>
+          <t>63018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156914</t>
+          <t>156584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165852</t>
+          <t>166037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83147</t>
+          <t>82441</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91848</t>
+          <t>91739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43360</t>
+          <t>43417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>122266</t>
+          <t>122055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132921</t>
+          <t>133256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32077</t>
+          <t>32007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82699</t>
+          <t>82140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93381</t>
+          <t>93188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37109</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45594</t>
+          <t>45925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122781</t>
+          <t>122851</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137129</t>
+          <t>136580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33197</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51510</t>
+          <t>52175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59553</t>
+          <t>59499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24222</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102942</t>
+          <t>104488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184829</t>
+          <t>184164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203142</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266590</t>
+          <t>266644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321513</t>
+          <t>321317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459539</t>
+          <t>457993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>538259</t>
+          <t>538338</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50080</t>
+          <t>49845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66427</t>
+          <t>66374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61240</t>
+          <t>61275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82028</t>
+          <t>82117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73592</t>
+          <t>73020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83446</t>
+          <t>83098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136839</t>
+          <t>136892</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153186</t>
+          <t>153421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213244</t>
+          <t>213155</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234032</t>
+          <t>233997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73349</t>
+          <t>73745</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96450</t>
+          <t>96987</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73739</t>
+          <t>74514</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97663</t>
+          <t>97153</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222586</t>
+          <t>222049</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245687</t>
+          <t>245291</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>224577</t>
+          <t>225087</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>248501</t>
+          <t>247726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69872</t>
+          <t>70676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97367</t>
+          <t>96669</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98516</t>
+          <t>93815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237776</t>
+          <t>237972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>164455</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>313196</t>
+          <t>314725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>538827</t>
+          <t>539525</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>566322</t>
+          <t>565518</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>775362</t>
+          <t>775166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>914622</t>
+          <t>919323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1336137</t>
+          <t>1334608</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1470055</t>
+          <t>1484878</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/BARTHEL_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1712</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51139</t>
+          <t>51319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>58990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>23157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78063</t>
+          <t>77527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87781</t>
+          <t>87565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>907</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47329</t>
+          <t>46212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>57155</t>
+          <t>57504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65497</t>
+          <t>65439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59889</t>
+          <t>60022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69155</t>
+          <t>69142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77811</t>
+          <t>78085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90262</t>
+          <t>90101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32456</t>
+          <t>32545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20998</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>40819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227616</t>
+          <t>227527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245164</t>
+          <t>245166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72347</t>
+          <t>71340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82661</t>
+          <t>82558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303356</t>
+          <t>305005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324826</t>
+          <t>324212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>27316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>17174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>36685</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>42183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67603</t>
+          <t>68934</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84835</t>
+          <t>85311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116193</t>
+          <t>115030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>135129</t>
+          <t>134541</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>41652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69927</t>
+          <t>70601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40545</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71356</t>
+          <t>72265</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355143</t>
+          <t>354469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>382985</t>
+          <t>383418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>357359</t>
+          <t>356450</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>388170</t>
+          <t>386137</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52277</t>
+          <t>53159</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109071</t>
+          <t>111199</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111958</t>
+          <t>110613</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155046</t>
+          <t>153564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>449274</t>
+          <t>448392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>471783</t>
+          <t>471247</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>567771</t>
+          <t>565643</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>603460</t>
+          <t>601344</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1023347</t>
+          <t>1024829</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1066435</t>
+          <t>1067780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33137</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56315</t>
+          <t>55793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68119</t>
+          <t>68084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17229</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47387</t>
+          <t>46333</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58709</t>
+          <t>59389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62302</t>
+          <t>61569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>75385</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>33084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99831</t>
+          <t>99499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113580</t>
+          <t>113407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35536</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48346</t>
+          <t>48310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140330</t>
+          <t>140184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159605</t>
+          <t>158940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>64097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>20965</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>48958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78742</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169486</t>
+          <t>167656</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196494</t>
+          <t>195686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39332</t>
+          <t>39130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51905</t>
+          <t>52434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213106</t>
+          <t>214066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243729</t>
+          <t>242890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51296</t>
+          <t>51013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77971</t>
+          <t>78328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65797</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96909</t>
+          <t>97362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77924</t>
+          <t>77975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93229</t>
+          <t>93177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110429</t>
+          <t>110072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137104</t>
+          <t>137387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194187</t>
+          <t>193734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225299</t>
+          <t>226021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79062</t>
+          <t>80658</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114756</t>
+          <t>115643</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79475</t>
+          <t>80583</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112808</t>
+          <t>116028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>279061</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315642</t>
+          <t>314046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>283884</t>
+          <t>280664</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>317217</t>
+          <t>316109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>67035</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>102984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168229</t>
+          <t>165839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>215483</t>
+          <t>217038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245762</t>
+          <t>245775</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309472</t>
+          <t>308054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>458396</t>
+          <t>456653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>494362</t>
+          <t>492602</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>526522</t>
+          <t>524967</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>573776</t>
+          <t>576166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>992170</t>
+          <t>993588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1055880</t>
+          <t>1055867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>59437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67878</t>
+          <t>67896</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92918</t>
+          <t>92408</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103380</t>
+          <t>103544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20667</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40360</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49868</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50265</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64400</t>
+          <t>64518</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17773</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102488</t>
+          <t>101985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113944</t>
+          <t>113645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32699</t>
+          <t>32340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>42814</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138742</t>
+          <t>139145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154778</t>
+          <t>154841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>29919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>29427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174052</t>
+          <t>173937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190196</t>
+          <t>190197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>66906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86415</t>
+          <t>86187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248682</t>
+          <t>248555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273121</t>
+          <t>273475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>19733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>24068</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48693</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50078</t>
+          <t>48299</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79596</t>
+          <t>78645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107042</t>
+          <t>107019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126080</t>
+          <t>125488</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110857</t>
+          <t>112042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134066</t>
+          <t>135482</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225175</t>
+          <t>226126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>254693</t>
+          <t>256472</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77971</t>
+          <t>78506</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116582</t>
+          <t>117709</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77971</t>
+          <t>78506</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116582</t>
+          <t>117709</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296501</t>
+          <t>295374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>335112</t>
+          <t>334577</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>296501</t>
+          <t>295374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>335112</t>
+          <t>334577</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,0%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>56185</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144350</t>
+          <t>142024</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195689</t>
+          <t>195290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>210555</t>
+          <t>211340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>269768</t>
+          <t>269386</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>505276</t>
+          <t>505290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>535163</t>
+          <t>535143</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>576675</t>
+          <t>577074</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>628014</t>
+          <t>630340</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1093924</t>
+          <t>1094306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1153137</t>
+          <t>1152352</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>101562</t>
+          <t>114293</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>110266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104426</t>
+          <t>117349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60389</t>
+          <t>69150</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56598</t>
+          <t>64743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63018</t>
+          <t>71936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>161951</t>
+          <t>183443</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156584</t>
+          <t>177445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166037</t>
+          <t>187498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88151</t>
+          <t>97527</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82441</t>
+          <t>91644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91739</t>
+          <t>101123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40680</t>
+          <t>48269</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>43901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43417</t>
+          <t>51314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>128831</t>
+          <t>145796</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>122055</t>
+          <t>138090</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133256</t>
+          <t>150468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>55040</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>159755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>159755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141581</t>
+          <t>159755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>17469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24069</t>
+          <t>26292</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32007</t>
+          <t>35179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88588</t>
+          <t>98212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82140</t>
+          <t>91930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93188</t>
+          <t>103361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42201</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37588</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45925</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>130789</t>
+          <t>144149</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122851</t>
+          <t>135262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136580</t>
+          <t>151286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>45299</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33837</t>
+          <t>37051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52175</t>
+          <t>57229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59499</t>
+          <t>28968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>62596</t>
+          <t>67634</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>55668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104488</t>
+          <t>79929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>194087</t>
+          <t>212548</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184164</t>
+          <t>200618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>220796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>305799</t>
+          <t>107930</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266644</t>
+          <t>101297</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321317</t>
+          <t>113035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>499885</t>
+          <t>320478</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>457993</t>
+          <t>308183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>538338</t>
+          <t>332444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>236339</t>
+          <t>257847</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>236339</t>
+          <t>257847</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>236339</t>
+          <t>257847</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>326143</t>
+          <t>130265</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>326143</t>
+          <t>130265</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>326143</t>
+          <t>130265</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>562481</t>
+          <t>388112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>562481</t>
+          <t>388112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>562481</t>
+          <t>388112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>58103</t>
+          <t>63168</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49845</t>
+          <t>54239</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66374</t>
+          <t>72884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>71228</t>
+          <t>76544</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61275</t>
+          <t>65321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82117</t>
+          <t>87432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>87417</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73020</t>
+          <t>81865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83098</t>
+          <t>92213</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>145163</t>
+          <t>154975</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136892</t>
+          <t>145259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153421</t>
+          <t>163904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>224044</t>
+          <t>242393</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213155</t>
+          <t>231505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233997</t>
+          <t>253616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>203266</t>
+          <t>218143</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203266</t>
+          <t>218143</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203266</t>
+          <t>218143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>295272</t>
+          <t>318937</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>295272</t>
+          <t>318937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>295272</t>
+          <t>318937</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84354</t>
+          <t>92189</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73745</t>
+          <t>79093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96987</t>
+          <t>105338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>85446</t>
+          <t>93370</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74514</t>
+          <t>81157</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97153</t>
+          <t>106317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>234682</t>
+          <t>251135</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222049</t>
+          <t>237986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245291</t>
+          <t>264231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>236794</t>
+          <t>253230</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>225087</t>
+          <t>240283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>247726</t>
+          <t>265443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>319036</t>
+          <t>343324</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319036</t>
+          <t>343324</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>319036</t>
+          <t>343324</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>322240</t>
+          <t>346600</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>322240</t>
+          <t>346600</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>322240</t>
+          <t>346600</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>82814</t>
+          <t>87410</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70676</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96669</t>
+          <t>103991</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>184224</t>
+          <t>201905</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93815</t>
+          <t>184869</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237972</t>
+          <t>221175</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>267038</t>
+          <t>289315</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164455</t>
+          <t>266159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>314725</t>
+          <t>313798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>553380</t>
+          <t>612094</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>539525</t>
+          <t>595513</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>565518</t>
+          <t>625850</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>828914</t>
+          <t>677396</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>775166</t>
+          <t>658126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>919323</t>
+          <t>694432</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1382295</t>
+          <t>1289490</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1334608</t>
+          <t>1265007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1484878</t>
+          <t>1312646</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>636194</t>
+          <t>699504</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>636194</t>
+          <t>699504</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>636194</t>
+          <t>699504</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1013138</t>
+          <t>879301</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1013138</t>
+          <t>879301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1013138</t>
+          <t>879301</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1649333</t>
+          <t>1578805</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1649333</t>
+          <t>1578805</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1649333</t>
+          <t>1578805</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
